--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DB948B-DA82-4B89-A79D-00BC625E8ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50300890-C47E-4847-B8B8-D8569D6D2384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
   <si>
     <t>Exp#</t>
   </si>
@@ -57,7 +57,37 @@
     <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s8 --zip_out submission_residual_s8.zip --strength 8 --sigmas 1.0,2.0,4.0 --aggregation median</t>
   </si>
   <si>
-    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s12 --zip_out submission_residual_s12.zip --strength 12 --sigmas 1.0,2.0,4.0 --aggregation median</t>
+    <t>Not increased</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s2 --zip_out submission_residual_s2.zip --strength 2 --sigmas 1.0,2.0,4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4 --zip_out submission_residual_s4.zip --strength 4 --sigmas 1.0,2.0,4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s5 --zip_out submission_residual_s5.zip --strength 5 --sigmas 1.0,2.0,4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_mean --zip_out submission_residual_s4_mean.zip --strength 4 --sigmas 1.0,2.0,4.0 --aggregation mean</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_trimmed --zip_out submission_residual_s4_trimmed.zip --strength 4 --sigmas 1.0,2.0,4.0 --aggregation trimmed_mean</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_mask --zip_out submission_residual_s4_mask.zip --strength 4 --sigmas 1.0,2.0,4.0 --aggregation median --texture_mask</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig_large --zip_out submission_residual_s4_sig_large.zip --strength 4 --sigmas 2.0,4.0,8.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig_small --zip_out submission_residual_s4_sig_small.zip --strength 4 --sigmas 0.5,1.0,2.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_whiten --zip_out submission_residual_s4_whiten.zip --strength 4 --sigmas 1.0,2.0,4.0 --aggregation median --whiten_sources</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s45 --zip_out submission_residual_s45.zip --strength 4.5 --sigmas 1.0,2.0,4.0 --aggregation median</t>
   </si>
 </sst>
 </file>
@@ -401,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -424,79 +454,215 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3">
         <v>0.326096</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="3">
         <v>0.34516599999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.352603</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50300890-C47E-4847-B8B8-D8569D6D2384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E4A333-34CB-4862-9BA3-50B51F4A2078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>Exp#</t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s45 --zip_out submission_residual_s45.zip --strength 4.5 --sigmas 1.0,2.0,4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>Frequency Bandpass Forgery</t>
+  </si>
+  <si>
+    <t>python approach_frequency_bandpass_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submissions/submission_freq_s4 --zip_out submission_freq_s4.zip --strength 4</t>
   </si>
 </sst>
 </file>
@@ -431,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -661,6 +667,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E4A333-34CB-4862-9BA3-50B51F4A2078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3015561D-5835-407B-A7AB-EF303EF8D50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
   <si>
     <t>Exp#</t>
   </si>
@@ -88,12 +88,6 @@
   </si>
   <si>
     <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s45 --zip_out submission_residual_s45.zip --strength 4.5 --sigmas 1.0,2.0,4.0 --aggregation median</t>
-  </si>
-  <si>
-    <t>Frequency Bandpass Forgery</t>
-  </si>
-  <si>
-    <t>python approach_frequency_bandpass_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submissions/submission_freq_s4 --zip_out submission_freq_s4.zip --strength 4</t>
   </si>
 </sst>
 </file>
@@ -437,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -667,20 +661,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3015561D-5835-407B-A7AB-EF303EF8D50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F0D52A-E558-4180-9613-E1429D4E20B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>Exp#</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s45 --zip_out submission_residual_s45.zip --strength 4.5 --sigmas 1.0,2.0,4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig1 --zip_out submission_residual_s4_sig1.zip --strength 4 --sigmas 1.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig2 --zip_out submission_residual_s4_sig2.zip --strength 4 --sigmas 2.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig4 --zip_out submission_residual_s4_sig4.zip --strength 4 --sigmas 4.0 --aggregation median</t>
   </si>
 </sst>
 </file>
@@ -431,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -632,6 +641,9 @@
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -659,6 +671,48 @@
       </c>
       <c r="D16" s="3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.37154199999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F0D52A-E558-4180-9613-E1429D4E20B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6C8788-BA63-44B4-A467-AF385CC11D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="28">
   <si>
     <t>Exp#</t>
   </si>
@@ -97,6 +97,18 @@
   </si>
   <si>
     <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig4 --zip_out submission_residual_s4_sig4.zip --strength 4 --sigmas 4.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig4_mean --zip_out submission_residual_s4_sig4_mean.zip --strength 4 --sigmas 4.0 --aggregation mean</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig4_trimmed --zip_out submission_residual_s4_sig4_trimmed.zip --strength 4 --sigmas 4.0 --aggregation trimmed_mean</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig4_whiten --zip_out submission_residual_s4_sig4_whiten.zip --strength 4 --sigmas 4.0 --aggregation median --whiten_sources</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig6 --zip_out submission_residual_s4_sig6.zip --strength 4 --sigmas 6.0 --aggregation median</t>
   </si>
 </sst>
 </file>
@@ -440,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -617,28 +629,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -659,60 +671,104 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D19" s="3">
         <v>0.37154199999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6C8788-BA63-44B4-A467-AF385CC11D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80993924-B515-4421-A6D7-076383061D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
   <si>
     <t>Exp#</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig6 --zip_out submission_residual_s4_sig6.zip --strength 4 --sigmas 6.0 --aggregation median</t>
+  </si>
+  <si>
+    <t>python approach_residual_fingerprint_forgery.py --zip_file Dataset.zip --dataset_dir Dataset --out_dir submission_temp_residual_s4_sig45 --zip_out submission_residual_s4_sig45.zip --strength 4 --sigmas 4.5 --aggregation median</t>
+  </si>
+  <si>
+    <t>with strength 4.2 and sigma 4</t>
+  </si>
+  <si>
+    <t>with strength 3.8 and sigma 4</t>
   </si>
 </sst>
 </file>
@@ -452,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -727,48 +736,102 @@
         <v>0.37154199999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80993924-B515-4421-A6D7-076383061D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7CC86A-02D7-4A58-86CC-AB1D20126B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="42">
   <si>
     <t>Exp#</t>
   </si>
@@ -118,6 +118,39 @@
   </si>
   <si>
     <t>with strength 3.8 and sigma 4</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0325</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f1_b0418</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0418_luma</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0418</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f085_b0418</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r38_f075_b0418</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f09_b0418</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f065_b0418</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0416</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0420</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
   </si>
 </sst>
 </file>
@@ -461,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -834,6 +867,160 @@
         <v>10</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.37529899999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.38280999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>33</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.38447100000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0.38536700000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7CC86A-02D7-4A58-86CC-AB1D20126B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43327442-81DD-4F08-B18F-AA23957750EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="45">
   <si>
     <t>Exp#</t>
   </si>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>Hybrid</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0516</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r4_f075_b0518</t>
+  </si>
+  <si>
+    <t>submission_hybrid_r42_f075_b0418</t>
   </si>
 </sst>
 </file>
@@ -494,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1021,6 +1030,48 @@
         <v>0.38536700000000002</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43327442-81DD-4F08-B18F-AA23957750EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CA2FD9-727A-4269-BDC0-8806B93E6B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
   <si>
     <t>Exp#</t>
   </si>
@@ -160,6 +160,18 @@
   </si>
   <si>
     <t>submission_hybrid_r42_f075_b0418</t>
+  </si>
+  <si>
+    <t>Per-WM adaptive</t>
+  </si>
+  <si>
+    <t>submission_per_wm_consistency_v3</t>
+  </si>
+  <si>
+    <t>submission_per_wm_consistency_v2</t>
+  </si>
+  <si>
+    <t>submission_per_wm_consistency_v1</t>
   </si>
 </sst>
 </file>
@@ -503,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1072,6 +1084,48 @@
         <v>10</v>
       </c>
     </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.41209400000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.4204</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>43</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.44159399999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CA2FD9-727A-4269-BDC0-8806B93E6B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FCFD7F-ACAF-46AB-9085-C0CB7968B6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
   <si>
     <t>Exp#</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>submission_per_wm_consistency_v1</t>
+  </si>
+  <si>
+    <t>submission_patch_balanced</t>
+  </si>
+  <si>
+    <t>Patch wm4 wm6 artifacts</t>
   </si>
 </sst>
 </file>
@@ -221,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +240,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1126,8 +1135,22 @@
         <v>0.44159399999999999</v>
       </c>
     </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>44</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0.44165500000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FCFD7F-ACAF-46AB-9085-C0CB7968B6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45512013-FFFB-42C1-A454-73CD0AB616F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="52">
   <si>
     <t>Exp#</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Patch wm4 wm6 artifacts</t>
+  </si>
+  <si>
+    <t>submission_patch_conservative</t>
   </si>
 </sst>
 </file>
@@ -524,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1149,6 +1152,20 @@
         <v>0.44165500000000002</v>
       </c>
     </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0.44313599999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45512013-FFFB-42C1-A454-73CD0AB616F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AAC717-5133-4E2D-AB5E-5C72676BDE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
   <si>
     <t>Exp#</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>submission_patch_conservative</t>
+  </si>
+  <si>
+    <t>submission_patch_aggressive</t>
   </si>
 </sst>
 </file>
@@ -527,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1166,6 +1169,20 @@
         <v>0.44313599999999997</v>
       </c>
     </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>46</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AAC717-5133-4E2D-AB5E-5C72676BDE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DB79A3-5EBA-4F91-B80B-B532D3A88462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
   <si>
     <t>Exp#</t>
   </si>
@@ -184,6 +184,30 @@
   </si>
   <si>
     <t>submission_patch_aggressive</t>
+  </si>
+  <si>
+    <t>submission_temp_wm4_edge_only</t>
+  </si>
+  <si>
+    <t>submission_wm6_peak_only</t>
+  </si>
+  <si>
+    <t>submission_wm4_edge_s035_all</t>
+  </si>
+  <si>
+    <t>submission_wm4_edge_s020_sides</t>
+  </si>
+  <si>
+    <t>WM 4 Edge only</t>
+  </si>
+  <si>
+    <t>WM 6 Peak only</t>
+  </si>
+  <si>
+    <t>WM 4 Edge s035 all</t>
+  </si>
+  <si>
+    <t>WM 4 Edge s020 sides</t>
   </si>
 </sst>
 </file>
@@ -530,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1183,6 +1207,62 @@
         <v>10</v>
       </c>
     </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0.44451600000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>48</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>49</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DB79A3-5EBA-4F91-B80B-B532D3A88462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F607D97-0C4B-48A1-8154-AFB372CB76C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="66">
   <si>
     <t>Exp#</t>
   </si>
@@ -208,6 +208,21 @@
   </si>
   <si>
     <t>WM 4 Edge s020 sides</t>
+  </si>
+  <si>
+    <t>wm4 Edge and wm6 Peak</t>
+  </si>
+  <si>
+    <t>python approach_patch_wm4_wm6_artifacts.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_per_wm_consistency_v1.zip --out_dir wm4_edge_wm6_peak --zip_out wm4_edge_wm6_peak.zip --profile wm4_edge_wm6_peak --print_psnr</t>
+  </si>
+  <si>
+    <t>python approach_patch_wm4_wm6_artifacts.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_per_wm_consistency_v1.zip --out_dir wm4_edge_wm6_peak_2 --zip_out wm4_edge_wm6_peak_2.zip --profile wm4_edge_wm6_peak_2 --print_psnr</t>
+  </si>
+  <si>
+    <t>python approach_patch_wm4_wm6_artifacts.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_per_wm_consistency_v1.zip --out_dir wm4_edge_wm6_peak_3 --zip_out wm4_edge_wm6_peak_3.zip --profile wm4_edge_wm6_peak_3 --print_psnr</t>
+  </si>
+  <si>
+    <t>python approach_patch_wm4_wm6_artifacts.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_per_wm_consistency_v1.zip --out_dir wm4_edge_wm6_peak_4 --zip_out wm4_edge_wm6_peak_4.zip --profile wm4_edge_wm6_peak_4 --print_psnr</t>
   </si>
 </sst>
 </file>
@@ -554,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1263,6 +1278,62 @@
         <v>10</v>
       </c>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>51</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>53</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DB79A3-5EBA-4F91-B80B-B532D3A88462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8819131C-077E-467D-825A-F22C1B9A5267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
   <si>
     <t>Exp#</t>
   </si>
@@ -208,6 +208,90 @@
   </si>
   <si>
     <t>WM 4 Edge s020 sides</t>
+  </si>
+  <si>
+    <t>submission_wm4_edge_s025_sides</t>
+  </si>
+  <si>
+    <t>submission_wm4_edge_s035_bottomcorners</t>
+  </si>
+  <si>
+    <t>WM 4 Edge s025 sides</t>
+  </si>
+  <si>
+    <t>WM 4 Edge s035 bottomcorners</t>
+  </si>
+  <si>
+    <t>submission_wm4_edge_s035_sides</t>
+  </si>
+  <si>
+    <t>WM 4 Edge s035 sides</t>
+  </si>
+  <si>
+    <t>submission_wm4_edge_s015_sides</t>
+  </si>
+  <si>
+    <t>WM 4 Edge s015 sides</t>
+  </si>
+  <si>
+    <t>submission_wm1_global_revert_sig4</t>
+  </si>
+  <si>
+    <t>WM1 sig4 last best</t>
+  </si>
+  <si>
+    <t>submission_wm1_no_freq</t>
+  </si>
+  <si>
+    <t>submission_wm1_sig6_s35</t>
+  </si>
+  <si>
+    <t>submission_wm1_sig8</t>
+  </si>
+  <si>
+    <t>submission_wm1_freq_narrow</t>
+  </si>
+  <si>
+    <t>submission_wm2_global_revert_sig4</t>
+  </si>
+  <si>
+    <t>WM 2 global revert sig4</t>
+  </si>
+  <si>
+    <t>WM 1 No Frew</t>
+  </si>
+  <si>
+    <t>WM1 sig6 s35</t>
+  </si>
+  <si>
+    <t>WM1 sig8</t>
+  </si>
+  <si>
+    <t>WM1 freq narrow</t>
+  </si>
+  <si>
+    <t>WM2 no freq</t>
+  </si>
+  <si>
+    <t>submission_wm2_no_freq</t>
+  </si>
+  <si>
+    <t>submission_wm2_freq_narrow</t>
+  </si>
+  <si>
+    <t>WM2 freq narrow</t>
+  </si>
+  <si>
+    <t>submission_wm2_sig6_s35</t>
+  </si>
+  <si>
+    <t>submission_wm2_sig8</t>
+  </si>
+  <si>
+    <t>wm2 sig8</t>
+  </si>
+  <si>
+    <t>wm2 sig6 S35</t>
   </si>
 </sst>
 </file>
@@ -554,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1263,6 +1347,202 @@
         <v>10</v>
       </c>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>51</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>53</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>55</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>56</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>57</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>58</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>59</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>60</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.44519700000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>61</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>62</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>63</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>64</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8819131C-077E-467D-825A-F22C1B9A5267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB3B3AF-607F-4330-BE85-F75A1C5BF0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
   <si>
     <t>Exp#</t>
   </si>
@@ -292,6 +292,30 @@
   </si>
   <si>
     <t>wm2 sig6 S35</t>
+  </si>
+  <si>
+    <t>submission_wm3_ms_tone</t>
+  </si>
+  <si>
+    <t>submission_wm3_luma_strong</t>
+  </si>
+  <si>
+    <t>submission_wm3_ms_balanced</t>
+  </si>
+  <si>
+    <t>submission_wm3_highfreq_plus</t>
+  </si>
+  <si>
+    <t>submission_wm3_vignette_focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wm3 </t>
+  </si>
+  <si>
+    <t>submission_wm3_freq_narrow</t>
+  </si>
+  <si>
+    <t>submission_wm3_sig8</t>
   </si>
 </sst>
 </file>
@@ -638,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1543,6 +1567,118 @@
         <v>10</v>
       </c>
     </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>65</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>66</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>67</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>68</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>69</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>70</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>71</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="3">
+        <v>0.44581100000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>72</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" s="3">
+        <v>0.44808900000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB3B3AF-607F-4330-BE85-F75A1C5BF0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D8D0CB-75D0-41F1-8A27-4062EDC470DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="106">
   <si>
     <t>Exp#</t>
   </si>
@@ -316,6 +316,33 @@
   </si>
   <si>
     <t>submission_wm3_sig8</t>
+  </si>
+  <si>
+    <t>wm_5678</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_wm3_sig8.zip --wm WM_8 --profile wm8_sig8 --out_dir submission_temp_wm8_sig8 --zip_out submission_wm8_sig8.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm8_sig8.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_wm3_sig8.zip --wm WM_8 --profile wm8_sig10 --out_dir submission_temp_wm8_sig10 --zip_out submission_wm8_sig10.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm8_sig10.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_wm8_sig10.zip --wm WM_5 --profile wm5_sig2 --out_dir submission_temp_wm5_sig2 --zip_out submission_wm5_sig2.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm5_sig2.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_wm8_sig10.zip --wm WM_5 --profile wm5_sig1_2 --out_dir submission_temp_wm5_sig1_2 --zip_out submission_wm5_sig1_2.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm5_sig1_2.zip</t>
   </si>
 </sst>
 </file>
@@ -365,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -381,6 +408,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1567,7 +1600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>65</v>
       </c>
@@ -1581,7 +1614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>66</v>
       </c>
@@ -1595,7 +1628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>67</v>
       </c>
@@ -1609,7 +1642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>68</v>
       </c>
@@ -1623,7 +1656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>69</v>
       </c>
@@ -1637,7 +1670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>70</v>
       </c>
@@ -1651,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>71</v>
       </c>
@@ -1665,7 +1698,7 @@
         <v>0.44581100000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>72</v>
       </c>
@@ -1677,6 +1710,68 @@
       </c>
       <c r="D72" s="3">
         <v>0.44808900000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>73</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="3">
+        <v>0.44998199999999999</v>
+      </c>
+      <c r="E73" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>74</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="3">
+        <v>0.45707799999999998</v>
+      </c>
+      <c r="E74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>75</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E75" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>76</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E76" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D8D0CB-75D0-41F1-8A27-4062EDC470DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB5A395-AFE7-4F6A-87E6-76ED88DC6CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="106">
   <si>
     <t>Exp#</t>
   </si>
@@ -1756,6 +1756,9 @@
       <c r="C75" s="6" t="s">
         <v>102</v>
       </c>
+      <c r="D75" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E75" t="s">
         <v>103</v>
       </c>
@@ -1769,6 +1772,9 @@
       </c>
       <c r="C76" s="7" t="s">
         <v>104</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>105</v>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB5A395-AFE7-4F6A-87E6-76ED88DC6CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990BB9EE-57D0-4A80-884C-F6AD07A570C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="110">
   <si>
     <t>Exp#</t>
   </si>
@@ -343,6 +343,18 @@
   </si>
   <si>
     <t>submission_wm5_sig1_2.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_wm8_sig10.zip --wm WM_8 --profile wm8_sig12 --out_dir submission_temp_wm8_sig12 --zip_out submission_wm8_sig12.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm8_sig12.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip submission_wm8_sig10.zip --wm WM_5 --profile wm5_sig8 --out_dir submission_temp_wm5_sig8 --zip_out submission_wm5_sig8.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm5_sig8.zip</t>
   </si>
 </sst>
 </file>
@@ -695,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1780,6 +1792,37 @@
         <v>105</v>
       </c>
     </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>77</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" t="s">
+        <v>106</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>78</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E78" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990BB9EE-57D0-4A80-884C-F6AD07A570C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F577B606-B4BC-46D6-AB0E-139D8D5BD00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="111">
   <si>
     <t>Exp#</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>submission_wm5_sig8.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm3_only_conservative.py  --zip_file Dataset.zip  --dataset_dir Dataset --base_zip latest_best_result.zip  --profile wm3_sig10  --out_dir submission_temp_wm3_sig10_from_wm2  --zip_out submission_wm3_sig10_from_wm2.zip  --print_psnr</t>
   </si>
 </sst>
 </file>
@@ -707,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1823,6 +1826,20 @@
         <v>109</v>
       </c>
     </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>79</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D79" s="3">
+        <v>0.45798800000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F577B606-B4BC-46D6-AB0E-139D8D5BD00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952E8C4F-0D73-420D-A645-025F7916445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="120">
   <si>
     <t>Exp#</t>
   </si>
@@ -358,6 +358,33 @@
   </si>
   <si>
     <t>python approach_wm3_only_conservative.py  --zip_file Dataset.zip  --dataset_dir Dataset --base_zip latest_best_result.zip  --profile wm3_sig10  --out_dir submission_temp_wm3_sig10_from_wm2  --zip_out submission_wm3_sig10_from_wm2.zip  --print_psnr</t>
+  </si>
+  <si>
+    <t>python approach_wm3_only_conservative.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm3_sig12 --out_dir submission_temp_wm3_sig12 --zip_out submission_wm3_sig12.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm3_sig12.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm1_only_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm1_sig10 --out_dir submission_temp_wm1_sig10 --zip_out submission_wm1_sig10.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm1_sig10.zip</t>
+  </si>
+  <si>
+    <t>wm1</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_6 --profile wm6_sig8 --out_dir submission_temp_wm6_sig8 --zip_out submission_wm6_sig8.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm6_sig8.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_7 --profile wm7_sig8 --out_dir submission_temp_wm7_sig8 --zip_out submission_wm7_sig8.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm7_sig8.zip</t>
   </si>
 </sst>
 </file>
@@ -710,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1822,6 +1849,9 @@
       <c r="C78" s="7" t="s">
         <v>108</v>
       </c>
+      <c r="D78" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E78" t="s">
         <v>109</v>
       </c>
@@ -1838,6 +1868,74 @@
       </c>
       <c r="D79" s="3">
         <v>0.45798800000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>80</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>81</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>82</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>83</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" s="3">
+        <v>0.463287</v>
+      </c>
+      <c r="E83" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952E8C4F-0D73-420D-A645-025F7916445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C60696-21B5-4FBF-9E50-72783D7441F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="128">
   <si>
     <t>Exp#</t>
   </si>
@@ -385,13 +385,37 @@
   </si>
   <si>
     <t>submission_wm7_sig8.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_7 --profile wm7_sig10 --out_dir submission_temp_wm7_sig10 --zip_out submission_wm7_sig10.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm7_sig10.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_6 --profile wm6_sig4 --out_dir submission_temp_wm6_sig4 --zip_out submission_wm6_sig4.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm6_sig4.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_5 --profile wm5_sig4 --out_dir submission_temp_wm5_sig4 --zip_out submission_wm5_sig4.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm5_sig4.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm1_only_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm1_sig6_s35 --out_dir submission_temp_wm1_sig6_s35 --zip_out submission_wm1_sig6_s35.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm1_sig6_s35.zip</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +427,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -445,9 +475,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -455,6 +482,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,12 +767,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="2" width="44.42578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="107.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="107.5703125" style="6" customWidth="1"/>
     <col min="4" max="4" width="16" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -753,7 +783,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -767,7 +797,7 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3">
@@ -781,7 +811,7 @@
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="3">
@@ -795,7 +825,7 @@
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -809,7 +839,7 @@
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -823,7 +853,7 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -837,7 +867,7 @@
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -851,7 +881,7 @@
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="3">
@@ -865,7 +895,7 @@
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -879,7 +909,7 @@
       <c r="B10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -893,7 +923,7 @@
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -907,7 +937,7 @@
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -921,7 +951,7 @@
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -935,7 +965,7 @@
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -949,7 +979,7 @@
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -963,7 +993,7 @@
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -977,7 +1007,7 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -991,7 +1021,7 @@
       <c r="B18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -1005,7 +1035,7 @@
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D19" s="3">
@@ -1019,7 +1049,7 @@
       <c r="B20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1033,7 +1063,7 @@
       <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -1047,7 +1077,7 @@
       <c r="B22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -1061,7 +1091,7 @@
       <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -1075,7 +1105,7 @@
       <c r="B24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -1089,7 +1119,7 @@
       <c r="B25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -1103,7 +1133,7 @@
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -1117,7 +1147,7 @@
       <c r="B27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D27" s="3">
@@ -1131,7 +1161,7 @@
       <c r="B28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -1145,7 +1175,7 @@
       <c r="B29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -1159,7 +1189,7 @@
       <c r="B30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="3">
@@ -1173,7 +1203,7 @@
       <c r="B31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -1187,7 +1217,7 @@
       <c r="B32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -1201,7 +1231,7 @@
       <c r="B33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -1215,7 +1245,7 @@
       <c r="B34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -1229,7 +1259,7 @@
       <c r="B35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -1243,7 +1273,7 @@
       <c r="B36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="3">
@@ -1257,7 +1287,7 @@
       <c r="B37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D37" s="3">
@@ -1271,7 +1301,7 @@
       <c r="B38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -1285,7 +1315,7 @@
       <c r="B39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -1299,7 +1329,7 @@
       <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -1313,7 +1343,7 @@
       <c r="B41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="3">
@@ -1327,7 +1357,7 @@
       <c r="B42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D42" s="3">
@@ -1341,7 +1371,7 @@
       <c r="B43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D43" s="3">
@@ -1352,10 +1382,10 @@
       <c r="A44" s="3">
         <v>44</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D44" s="3">
@@ -1366,10 +1396,10 @@
       <c r="A45" s="3">
         <v>45</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D45" s="3">
@@ -1380,10 +1410,10 @@
       <c r="A46" s="3">
         <v>46</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -1397,7 +1427,7 @@
       <c r="B47" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D47" s="3">
@@ -1411,7 +1441,7 @@
       <c r="B48" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -1425,7 +1455,7 @@
       <c r="B49" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -1481,7 +1511,7 @@
       <c r="B53" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -1495,7 +1525,7 @@
       <c r="B54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -1509,7 +1539,7 @@
       <c r="B55" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -1523,7 +1553,7 @@
       <c r="B56" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -1537,7 +1567,7 @@
       <c r="B57" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>72</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -1551,7 +1581,7 @@
       <c r="B58" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -1565,7 +1595,7 @@
       <c r="B59" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -1579,7 +1609,7 @@
       <c r="B60" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D60" s="3">
@@ -1593,7 +1623,7 @@
       <c r="B61" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>82</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -1607,7 +1637,7 @@
       <c r="B62" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -1621,7 +1651,7 @@
       <c r="B63" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -1635,7 +1665,7 @@
       <c r="B64" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -1649,7 +1679,7 @@
       <c r="B65" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -1663,7 +1693,7 @@
       <c r="B66" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>90</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -1677,7 +1707,7 @@
       <c r="B67" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -1691,7 +1721,7 @@
       <c r="B68" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -1705,7 +1735,7 @@
       <c r="B69" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -1719,7 +1749,7 @@
       <c r="B70" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -1733,7 +1763,7 @@
       <c r="B71" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D71" s="3">
@@ -1747,7 +1777,7 @@
       <c r="B72" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="3">
@@ -1761,7 +1791,7 @@
       <c r="B73" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="5" t="s">
         <v>98</v>
       </c>
       <c r="D73" s="3">
@@ -1778,7 +1808,7 @@
       <c r="B74" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="5" t="s">
         <v>100</v>
       </c>
       <c r="D74" s="3">
@@ -1795,7 +1825,7 @@
       <c r="B75" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -1812,7 +1842,7 @@
       <c r="B76" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="6" t="s">
         <v>104</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -1829,7 +1859,7 @@
       <c r="B77" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="5" t="s">
         <v>106</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -1846,7 +1876,7 @@
       <c r="B78" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>108</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -1863,7 +1893,7 @@
       <c r="B79" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="6" t="s">
         <v>110</v>
       </c>
       <c r="D79" s="3">
@@ -1877,7 +1907,7 @@
       <c r="B80" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="6" t="s">
         <v>111</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -1894,7 +1924,7 @@
       <c r="B81" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="6" t="s">
         <v>113</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -1911,7 +1941,7 @@
       <c r="B82" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="6" t="s">
         <v>116</v>
       </c>
       <c r="D82" s="3" t="s">
@@ -1928,7 +1958,7 @@
       <c r="B83" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="6" t="s">
         <v>118</v>
       </c>
       <c r="D83" s="3">
@@ -1938,7 +1968,76 @@
         <v>119</v>
       </c>
     </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>84</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>85</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>86</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>87</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C60696-21B5-4FBF-9E50-72783D7441F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F10145E-9466-4DFF-86BC-1E6BBC5B2CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="134">
   <si>
     <t>Exp#</t>
   </si>
@@ -409,6 +409,24 @@
   </si>
   <si>
     <t>submission_wm1_sig6_s35.zip</t>
+  </si>
+  <si>
+    <t>submission_wm7_sig8_no_freq.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_7 --profile wm7_sig8_no_freq --out_dir submission_temp_wm7_sig8_no_freq --zip_out submission_wm7_sig8_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_7 --profile wm7_sig8_s35 --out_dir submission_temp_wm7_sig8_s35 --zip_out submission_wm7_sig8_s35.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm7_sig8_s35.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_7 --profile wm7_sig8_s45 --out_dir submission_temp_wm7_sig8_s45 --zip_out submission_wm7_sig8_s45.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm7_sig8_s45.zip</t>
   </si>
 </sst>
 </file>
@@ -767,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2036,6 +2054,57 @@
         <v>127</v>
       </c>
     </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>88</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>89</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>90</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F10145E-9466-4DFF-86BC-1E6BBC5B2CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F6335-1C35-4960-83AC-7EE208E2B1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="140">
   <si>
     <t>Exp#</t>
   </si>
@@ -427,6 +427,24 @@
   </si>
   <si>
     <t>submission_wm7_sig8_s45.zip</t>
+  </si>
+  <si>
+    <t>submission_wm8_sig10_s35.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_8 --profile wm8_sig10_s35 --out_dir submission_temp_wm8_sig10_s35 --zip_out submission_wm8_sig10_s35.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_8 --profile wm8_sig10_s45 --out_dir submission_temp_wm8_sig10_s45 --zip_out submission_wm8_sig10_s45.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm8_sig10_s45.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_8 --profile wm8_sig10_no_freq --out_dir submission_temp_wm8_sig10_no_freq --zip_out submission_wm8_sig10_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm8_sig10_no_freq.zip</t>
   </si>
 </sst>
 </file>
@@ -785,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2105,6 +2123,57 @@
         <v>133</v>
       </c>
     </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>91</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>92</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>93</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D93" s="3">
+        <v>0.46473599999999998</v>
+      </c>
+      <c r="E93" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F6335-1C35-4960-83AC-7EE208E2B1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1931587-8B53-4EAF-85DB-69929325A6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="152">
   <si>
     <t>Exp#</t>
   </si>
@@ -445,6 +445,42 @@
   </si>
   <si>
     <t>submission_wm8_sig10_no_freq.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm3_only_conservative.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm3_sig10_s35 --out_dir submission_temp_wm3_sig10_s35 --zip_out submission_wm3_sig10_s35.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm3_sig10_s35.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm3_only_conservative.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm3_sig10_s45 --out_dir submission_temp_wm3_sig10_s45 --zip_out submission_wm3_sig10_s45.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm3_sig10_s45.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm3_only_conservative.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm3_sig10_s50 --out_dir submission_temp_wm3_sig10_s50 --zip_out submission_wm3_sig10_s50.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm3_sig10_s50.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm3_only_conservative.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm3_sig10_no_freq --out_dir submission_temp_wm3_sig10_no_freq --zip_out submission_wm3_sig10_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm3_sig10_no_freq.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm1_only_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm1_no_freq --out_dir submission_temp_wm1_no_freq --zip_out submission_wm1_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm1_no_freq.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_6 --profile wm6_no_freq --out_dir submission_temp_wm6_no_freq --zip_out submission_wm6_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm6_no_freq.zip</t>
   </si>
 </sst>
 </file>
@@ -803,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2174,6 +2210,108 @@
         <v>139</v>
       </c>
     </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>94</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>95</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>96</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>97</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
+        <v>98</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>99</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D99" s="3">
+        <v>0.46500799999999998</v>
+      </c>
+      <c r="E99" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1931587-8B53-4EAF-85DB-69929325A6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D80E926-55A4-49DF-AD72-AA2C6CA7A4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="157">
   <si>
     <t>Exp#</t>
   </si>
@@ -481,6 +481,21 @@
   </si>
   <si>
     <t>submission_wm6_no_freq.zip</t>
+  </si>
+  <si>
+    <t>submission_wm5_no_freq.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_5 --profile wm5_no_freq --out_dir submission_temp_wm5_no_freq --zip_out submission_wm5_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>wm2</t>
+  </si>
+  <si>
+    <t>python approach_wm2_only_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --profile wm2_sig4_no_freq --out_dir submission_temp_wm2_sig4_no_freq --zip_out submission_wm2_sig4_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm2_sig4_no_freq.zip</t>
   </si>
 </sst>
 </file>
@@ -839,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2312,6 +2327,40 @@
         <v>151</v>
       </c>
     </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>100</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>101</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D101" s="3">
+        <v>0.46557500000000002</v>
+      </c>
+      <c r="E101" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D80E926-55A4-49DF-AD72-AA2C6CA7A4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7315F740-79E4-4088-A0F0-1F643B43631F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="159">
   <si>
     <t>Exp#</t>
   </si>
@@ -496,6 +496,12 @@
   </si>
   <si>
     <t>submission_wm2_sig4_no_freq.zip</t>
+  </si>
+  <si>
+    <t>python approach_wm5678_experiments.py --zip_file Dataset.zip --dataset_dir Dataset --base_zip latest_best_result.zip --wm WM_6 --profile wm6_sig6_no_freq --out_dir submission_temp_wm6_sig6_no_freq --zip_out submission_wm6_sig6_no_freq.zip --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm6_sig6_no_freq.zip</t>
   </si>
 </sst>
 </file>
@@ -854,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2361,6 +2367,23 @@
         <v>156</v>
       </c>
     </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>102</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D102" s="3">
+        <v>0.46648600000000001</v>
+      </c>
+      <c r="E102" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UdS\Summer 2026\courses\TML\assignments\Assignment 4\tml2026-team_XLIII-assignment_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7315F740-79E4-4088-A0F0-1F643B43631F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B4E411-0A77-4C32-82B5-1F839D838720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="162">
   <si>
     <t>Exp#</t>
   </si>
@@ -502,6 +502,15 @@
   </si>
   <si>
     <t>submission_wm6_sig6_no_freq.zip</t>
+  </si>
+  <si>
+    <t>submission_wm6_peaklock_s35</t>
+  </si>
+  <si>
+    <t>submission_wm7_peaklock_s35</t>
+  </si>
+  <si>
+    <t>submission_wm8_peaklock_s35</t>
   </si>
 </sst>
 </file>
@@ -860,13 +869,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="2" width="44.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="107.5703125" style="6" customWidth="1"/>
     <col min="4" max="4" width="16" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2382,6 +2392,39 @@
       </c>
       <c r="E102" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>103</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>104</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>105</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B4E411-0A77-4C32-82B5-1F839D838720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1D891C-8F8B-42A4-81CD-6E8663197E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="168">
   <si>
     <t>Exp#</t>
   </si>
@@ -511,6 +511,40 @@
   </si>
   <si>
     <t>submission_wm8_peaklock_s35</t>
+  </si>
+  <si>
+    <t>python approach_dwtdct_real_scheme.py \
+  --zip_file Dataset.zip \
+  --dataset_dir Dataset \
+  --base_zip latest_best_result.zip \
+  --out_dir submission_temp_wm1_dwtdct \
+  --zip_out submission_wm1_dwtdct_real.zip \
+  --n_bits 32 \
+  --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm1_dwtdct_real</t>
+  </si>
+  <si>
+    <t>submission_wm2_real</t>
+  </si>
+  <si>
+    <t>python approach_real_scheme_forgery.py \
+  --zip_file Dataset.zip --dataset_dir Dataset \
+  --base_zip latest_best_results_0577.zip \
+  --out_dir temp_wm2_rivagan \
+  --zip_out submission_wm1_wm2_real.zip \
+  --wm WM_2 --method rivaGan --n_bits 32 --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm1_wm2_wm8_real</t>
+  </si>
+  <si>
+    <t>python approach_real_scheme_forgery.py \
+  --zip_file Dataset.zip --dataset_dir Dataset \
+  --base_zip submission_wm1_wm2_real.zip \
+  --out_dir temp_wm8_dwtdct --zip_out submission_wm1_wm2_wm8_real.zip \
+  --wm WM_8 --method dwtDct --n_bits 24 --print_psnr</t>
   </si>
 </sst>
 </file>
@@ -566,7 +600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -588,6 +622,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2427,6 +2464,48 @@
         <v>10</v>
       </c>
     </row>
+    <row r="106" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>106</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D106" s="3">
+        <v>0.57699999999999996</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>107</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D107" s="3">
+        <v>0.70099999999999996</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>108</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1D891C-8F8B-42A4-81CD-6E8663197E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA3CD2D-0A75-4158-8A7D-BA0DF7179229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="170">
   <si>
     <t>Exp#</t>
   </si>
@@ -545,6 +545,15 @@
   --base_zip submission_wm1_wm2_real.zip \
   --out_dir temp_wm8_dwtdct --zip_out submission_wm1_wm2_wm8_real.zip \
   --wm WM_8 --method dwtDct --n_bits 24 --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm7_trustmark</t>
+  </si>
+  <si>
+    <t>approach_trustmark_forgery.py \
+  --dataset_dir Dataset --base_zip latest_best_results_070.zip \
+  --out_dir temp_wm7 --zip_out submission_wm7_trustmark.zip \
+  --variant Q --print_psnr</t>
   </si>
 </sst>
 </file>
@@ -600,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -622,9 +631,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2464,46 +2470,60 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>106</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D106" s="3">
         <v>0.57699999999999996</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>107</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D107" s="3">
         <v>0.70099999999999996</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>108</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="6" t="s">
         <v>167</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>109</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D109" s="3">
+        <v>0.80372100000000002</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM 5\TML\Assignments\Watermarking\tml2026-team_XLIII-assignment_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA3CD2D-0A75-4158-8A7D-BA0DF7179229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40E8DFD-A462-4DFD-9E50-5F0059AF7909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="172">
   <si>
     <t>Exp#</t>
   </si>
@@ -554,6 +554,15 @@
   --dataset_dir Dataset --base_zip latest_best_results_070.zip \
   --out_dir temp_wm7 --zip_out submission_wm7_trustmark.zip \
   --variant Q --print_psnr</t>
+  </si>
+  <si>
+    <t>submission_wm8_trustmark</t>
+  </si>
+  <si>
+    <t>venv_trustmark/Scripts/python.exe approach_trustmark_forgery.py \
+  --dataset_dir Dataset --base_zip latest_best_results_080.zip \
+  --wm WM_8 --variant P \
+  --out_dir temp_wm8 --zip_out submission_wm8_trustmark.zip --print_psnr</t>
   </si>
 </sst>
 </file>
@@ -912,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -2526,6 +2535,20 @@
         <v>0.80372100000000002</v>
       </c>
     </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>110</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D110" s="3">
+        <v>0.90100000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
